--- a/examples/dogfood/output/workbook.xlsx
+++ b/examples/dogfood/output/workbook.xlsx
@@ -123,7 +123,7 @@
     <t>Architecture diagrams (IR)</t>
   </si>
   <si>
-    <t>D2 diagrams (studio only)</t>
+    <t>Visual diagram editor (draw.io)</t>
   </si>
   <si>
     <t>Measured text autofit</t>
